--- a/backend/data/Genus_Cost.xlsx
+++ b/backend/data/Genus_Cost.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
@@ -450,15 +450,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ServiceLocation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Genus</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Genus Cost</t>
         </is>
@@ -477,15 +482,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1.1-SUPPORT-TRAINEE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>520</v>
       </c>
     </row>
@@ -502,15 +512,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>1.1-TRAINEE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>620</v>
       </c>
     </row>
@@ -527,15 +542,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2.1-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>871</v>
       </c>
     </row>
@@ -552,15 +572,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2.1-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>852</v>
       </c>
     </row>
@@ -577,15 +602,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2.1-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>781</v>
       </c>
     </row>
@@ -602,15 +632,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>2.1-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>841</v>
       </c>
     </row>
@@ -627,15 +662,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>2.1-CUSTOM</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>771</v>
       </c>
     </row>
@@ -652,15 +692,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>2.1-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>775</v>
       </c>
     </row>
@@ -677,15 +722,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>2.1-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>968</v>
       </c>
     </row>
@@ -702,15 +752,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>2.1-DEVOPS</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>852</v>
       </c>
     </row>
@@ -727,15 +782,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>2.1-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>871</v>
       </c>
     </row>
@@ -752,15 +812,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>2.1-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>799</v>
       </c>
     </row>
@@ -777,15 +842,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>2.1-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>775</v>
       </c>
     </row>
@@ -802,15 +872,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>2.1-EMBEDDED</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>657</v>
       </c>
     </row>
@@ -827,15 +902,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>2.1-ERP</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>847</v>
       </c>
     </row>
@@ -852,15 +932,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>2.1-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>726</v>
       </c>
     </row>
@@ -877,15 +962,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>2.1-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>799</v>
       </c>
     </row>
@@ -902,15 +992,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>2.1-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>1017</v>
       </c>
     </row>
@@ -927,15 +1022,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>2.1-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>726</v>
       </c>
     </row>
@@ -952,15 +1052,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>2.1-INFRAOPS</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>726</v>
       </c>
     </row>
@@ -977,15 +1082,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>2.1-JAVA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>854</v>
       </c>
     </row>
@@ -1002,15 +1112,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>2.1-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>920</v>
       </c>
     </row>
@@ -1027,15 +1142,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>2.1-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>992</v>
       </c>
     </row>
@@ -1052,15 +1172,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>2.1-PHP</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>702</v>
       </c>
     </row>
@@ -1077,15 +1202,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>2.1-PYTHON</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>847</v>
       </c>
     </row>
@@ -1102,15 +1232,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>2.2-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>1025</v>
       </c>
     </row>
@@ -1127,15 +1262,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>2.2-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>1002</v>
       </c>
     </row>
@@ -1152,15 +1292,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>2.2-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>919</v>
       </c>
     </row>
@@ -1177,15 +1322,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>2.2-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>989</v>
       </c>
     </row>
@@ -1202,15 +1352,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>2.2-CUSTOM</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>907</v>
       </c>
     </row>
@@ -1227,15 +1382,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>2.2-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>911</v>
       </c>
     </row>
@@ -1252,15 +1412,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>2.2-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>1139</v>
       </c>
     </row>
@@ -1277,15 +1442,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>2.2-DEVOPS</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>1003</v>
       </c>
     </row>
@@ -1302,15 +1472,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>2.2-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>1025</v>
       </c>
     </row>
@@ -1327,15 +1502,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>2.2-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>940</v>
       </c>
     </row>
@@ -1352,15 +1532,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>2.2-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>911</v>
       </c>
     </row>
@@ -1377,15 +1562,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>2.2-EMBEDDED</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>772</v>
       </c>
     </row>
@@ -1402,15 +1592,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>2.2-ERP</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>997</v>
       </c>
     </row>
@@ -1427,15 +1622,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>2.2-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>854</v>
       </c>
     </row>
@@ -1452,15 +1652,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>2.2-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>940</v>
       </c>
     </row>
@@ -1477,15 +1682,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>2.2-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>1196</v>
       </c>
     </row>
@@ -1502,15 +1712,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>2.2-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>854</v>
       </c>
     </row>
@@ -1527,15 +1742,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>2.2-INFRAOPS</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>854</v>
       </c>
     </row>
@@ -1552,15 +1772,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>2.2-JAVA</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>1005</v>
       </c>
     </row>
@@ -1577,15 +1802,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>2.2-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
         <v>1082</v>
       </c>
     </row>
@@ -1602,15 +1832,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>2.2-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>1167</v>
       </c>
     </row>
@@ -1627,15 +1862,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>2.2-PHP</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
         <v>826</v>
       </c>
     </row>
@@ -1652,15 +1892,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>2.2-PYTHON</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>997</v>
       </c>
     </row>
@@ -1677,15 +1922,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>2.3-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
         <v>1206</v>
       </c>
     </row>
@@ -1702,15 +1952,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>2.3-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
         <v>1179</v>
       </c>
     </row>
@@ -1727,15 +1982,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>2.3-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
         <v>1081</v>
       </c>
     </row>
@@ -1752,15 +2012,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>2.3-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>1182</v>
       </c>
     </row>
@@ -1777,15 +2042,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>2.3-CUSTOM</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>1021</v>
       </c>
     </row>
@@ -1802,15 +2072,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>2.3-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
         <v>1072</v>
       </c>
     </row>
@@ -1827,15 +2102,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>2.3-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>1340</v>
       </c>
     </row>
@@ -1852,15 +2132,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>2.3-DEVOPS</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>1180</v>
       </c>
     </row>
@@ -1877,15 +2162,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>2.3-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>1206</v>
       </c>
     </row>
@@ -1902,15 +2192,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>2.3-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
         <v>1106</v>
       </c>
     </row>
@@ -1927,15 +2222,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>2.3-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>1072</v>
       </c>
     </row>
@@ -1952,15 +2252,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>2.3-EMBEDDED</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>909</v>
       </c>
     </row>
@@ -1977,15 +2282,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>2.3-ERP</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
         <v>1172</v>
       </c>
     </row>
@@ -2002,15 +2312,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>2.3-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
         <v>1005</v>
       </c>
     </row>
@@ -2027,15 +2342,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>2.3-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>1106</v>
       </c>
     </row>
@@ -2052,15 +2372,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>2.3-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
         <v>1407</v>
       </c>
     </row>
@@ -2077,15 +2402,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>2.3-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
         <v>1005</v>
       </c>
     </row>
@@ -2102,15 +2432,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>2.3-INFRAOPS</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
         <v>1005</v>
       </c>
     </row>
@@ -2127,15 +2462,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>2.3-JAVA</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
         <v>1182</v>
       </c>
     </row>
@@ -2152,15 +2492,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>2.3-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
         <v>1273</v>
       </c>
     </row>
@@ -2177,15 +2522,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>2.3-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
         <v>1374</v>
       </c>
     </row>
@@ -2202,15 +2552,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>2.3-PHP</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
         <v>972</v>
       </c>
     </row>
@@ -2227,15 +2582,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>2.3-PYTHON</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
         <v>1172</v>
       </c>
     </row>
@@ -2252,15 +2612,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>3.1-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -2277,15 +2642,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>3.1-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
         <v>1760</v>
       </c>
     </row>
@@ -2302,15 +2672,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>3.1-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
         <v>1613</v>
       </c>
     </row>
@@ -2327,15 +2702,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>3.1-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
         <v>1686</v>
       </c>
     </row>
@@ -2352,15 +2732,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>3.1-CUSTOM</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
         <v>1605</v>
       </c>
     </row>
@@ -2377,15 +2762,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>3.1-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -2402,15 +2792,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>3.1-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -2427,15 +2822,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>3.1-DEVOPS</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
         <v>1761</v>
       </c>
     </row>
@@ -2452,15 +2852,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>3.1-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -2477,15 +2882,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>3.1-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -2502,15 +2912,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>3.1-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -2527,15 +2942,20 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>3.1-EMBEDDED</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
         <v>1356</v>
       </c>
     </row>
@@ -2552,15 +2972,20 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>3.1-ERP</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
         <v>1750</v>
       </c>
     </row>
@@ -2577,15 +3002,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>3.1-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -2602,15 +3032,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
           <t>3.1-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -2627,15 +3062,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>3.1-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
         <v>2100</v>
       </c>
     </row>
@@ -2652,15 +3092,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>3.1-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -2677,15 +3122,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>3.1-INFRAOPS</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -2702,15 +3152,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>3.1-JAVA</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -2727,15 +3182,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>3.1-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
         <v>1900</v>
       </c>
     </row>
@@ -2752,15 +3212,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>3.1-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
         <v>2050</v>
       </c>
     </row>
@@ -2777,15 +3242,20 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>3.1-PHP</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
         <v>1450</v>
       </c>
     </row>
@@ -2802,15 +3272,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>3.1-PYTHON</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>1750</v>
       </c>
     </row>
@@ -2827,15 +3302,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>3.2-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
         <v>2142</v>
       </c>
     </row>
@@ -2852,15 +3332,20 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>3.2-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
         <v>2094</v>
       </c>
     </row>
@@ -2877,15 +3362,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>3.2-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
         <v>1920</v>
       </c>
     </row>
@@ -2902,15 +3392,20 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>3.2-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
         <v>2067</v>
       </c>
     </row>
@@ -2927,15 +3422,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>3.2-CUSTOM</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
         <v>1960</v>
       </c>
     </row>
@@ -2952,15 +3452,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>3.2-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>1904</v>
       </c>
     </row>
@@ -2977,15 +3482,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>3.2-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
         <v>2380</v>
       </c>
     </row>
@@ -3002,15 +3512,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
           <t>3.2-DEVOPS</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
         <v>2095.04</v>
       </c>
     </row>
@@ -3027,15 +3542,20 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>3.2-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
         <v>2142</v>
       </c>
     </row>
@@ -3052,15 +3572,20 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
           <t>3.2-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
         <v>1964</v>
       </c>
     </row>
@@ -3077,15 +3602,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>3.2-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
         <v>1904</v>
       </c>
     </row>
@@ -3102,15 +3632,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
           <t>3.2-EMBEDDED</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>1614</v>
       </c>
     </row>
@@ -3127,15 +3662,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>3.2-ERP</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>2082</v>
       </c>
     </row>
@@ -3152,15 +3692,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>3.2-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
         <v>1785</v>
       </c>
     </row>
@@ -3177,15 +3722,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
           <t>3.2-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
         <v>1964</v>
       </c>
     </row>
@@ -3202,15 +3752,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>3.2-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
         <v>2499</v>
       </c>
     </row>
@@ -3227,15 +3782,20 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
           <t>3.2-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
         <v>1785</v>
       </c>
     </row>
@@ -3252,15 +3812,20 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
           <t>3.2-INFRAOPS</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
         <v>1785</v>
       </c>
     </row>
@@ -3277,15 +3842,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
           <t>3.2-JAVA</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
         <v>2100</v>
       </c>
     </row>
@@ -3302,15 +3872,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>3.2-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
         <v>2261</v>
       </c>
     </row>
@@ -3327,15 +3902,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
           <t>3.2-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
         <v>2440</v>
       </c>
     </row>
@@ -3352,15 +3932,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>3.2-PHP</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
         <v>1726</v>
       </c>
     </row>
@@ -3377,15 +3962,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
           <t>3.2-PYTHON</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
         <v>2082</v>
       </c>
     </row>
@@ -3402,15 +3992,20 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
           <t>3.3-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
         <v>2592</v>
       </c>
     </row>
@@ -3427,15 +4022,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>3.3-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
         <v>2534</v>
       </c>
     </row>
@@ -3452,15 +4052,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
           <t>3.3-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
         <v>2323</v>
       </c>
     </row>
@@ -3477,15 +4082,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
           <t>3.3-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
         <v>2536</v>
       </c>
     </row>
@@ -3502,15 +4112,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
           <t>3.3-CUSTOM</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
         <v>2292</v>
       </c>
     </row>
@@ -3527,15 +4142,20 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
           <t>3.3-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
         <v>2304</v>
       </c>
     </row>
@@ -3552,15 +4172,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
           <t>3.3-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
         <v>2880</v>
       </c>
     </row>
@@ -3577,15 +4202,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
           <t>3.3-DEVOPS</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
         <v>2535</v>
       </c>
     </row>
@@ -3602,15 +4232,20 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>3.3-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
         <v>2592</v>
       </c>
     </row>
@@ -3627,15 +4262,20 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
           <t>3.3-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
         <v>2376</v>
       </c>
     </row>
@@ -3652,15 +4292,20 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
           <t>3.3-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>2304</v>
       </c>
     </row>
@@ -3677,15 +4322,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
           <t>3.3-EMBEDDED</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
         <v>1953</v>
       </c>
     </row>
@@ -3702,15 +4352,20 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>3.3-ERP</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
         <v>2520</v>
       </c>
     </row>
@@ -3727,15 +4382,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>3.3-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
         <v>2160</v>
       </c>
     </row>
@@ -3752,15 +4412,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
           <t>3.3-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
         <v>2376</v>
       </c>
     </row>
@@ -3777,15 +4442,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>3.3-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
         <v>3024</v>
       </c>
     </row>
@@ -3802,15 +4472,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
           <t>3.3-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
         <v>2160</v>
       </c>
     </row>
@@ -3827,15 +4502,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
           <t>3.3-INFRAOPS</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
         <v>2160</v>
       </c>
     </row>
@@ -3852,15 +4532,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>3.3-JAVA</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
         <v>2490.71</v>
       </c>
     </row>
@@ -3877,15 +4562,20 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>3.3-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
         <v>2736</v>
       </c>
     </row>
@@ -3902,15 +4592,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>3.3-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>2952</v>
       </c>
     </row>
@@ -3927,15 +4622,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>3.3-PHP</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
         <v>2088</v>
       </c>
     </row>
@@ -3952,15 +4652,20 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
           <t>3.3-PYTHON</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
         <v>2520</v>
       </c>
     </row>
@@ -3977,15 +4682,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
           <t>4.1-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
         <v>3369</v>
       </c>
     </row>
@@ -4002,15 +4712,20 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
           <t>4.1-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
         <v>3294</v>
       </c>
     </row>
@@ -4027,15 +4742,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
           <t>4.1-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
         <v>3020</v>
       </c>
     </row>
@@ -4052,15 +4772,20 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
           <t>4.1-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
         <v>3252</v>
       </c>
     </row>
@@ -4077,15 +4802,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
           <t>4.1-CUSTOM</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
         <v>2980</v>
       </c>
     </row>
@@ -4102,15 +4832,20 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
           <t>4.1-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
         <v>2995</v>
       </c>
     </row>
@@ -4127,15 +4862,20 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
           <t>4.1-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
         <v>3744</v>
       </c>
     </row>
@@ -4152,15 +4892,20 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
           <t>4.1-DEVOPS</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
         <v>3295</v>
       </c>
     </row>
@@ -4177,15 +4922,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
           <t>4.1-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
         <v>3369</v>
       </c>
     </row>
@@ -4202,15 +4952,20 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
           <t>4.1-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
         <v>3089</v>
       </c>
     </row>
@@ -4227,15 +4982,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
           <t>4.1-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
         <v>2995</v>
       </c>
     </row>
@@ -4252,15 +5012,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
           <t>4.1-EMBEDDED</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
         <v>2539</v>
       </c>
     </row>
@@ -4277,15 +5042,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
           <t>4.1-ERP</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
         <v>3276</v>
       </c>
     </row>
@@ -4302,15 +5072,20 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
           <t>4.1-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
         <v>2808</v>
       </c>
     </row>
@@ -4327,15 +5102,20 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
           <t>4.1-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
         <v>3089</v>
       </c>
     </row>
@@ -4352,15 +5132,20 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
           <t>4.1-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
         <v>3931</v>
       </c>
     </row>
@@ -4377,15 +5162,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
           <t>4.1-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
         <v>2808</v>
       </c>
     </row>
@@ -4402,15 +5192,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
           <t>4.1-INFRAOPS</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
         <v>2808</v>
       </c>
     </row>
@@ -4427,15 +5222,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
           <t>4.1-JAVA</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
         <v>3304</v>
       </c>
     </row>
@@ -4452,15 +5252,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
           <t>4.1-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
         <v>3557</v>
       </c>
     </row>
@@ -4477,15 +5282,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
           <t>4.1-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
         <v>3837</v>
       </c>
     </row>
@@ -4502,15 +5312,20 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
           <t>4.1-PHP</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
         <v>2714</v>
       </c>
     </row>
@@ -4527,15 +5342,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
           <t>4.1-PYTHON</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
         <v>3276</v>
       </c>
     </row>
@@ -4552,15 +5372,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
           <t>4.2-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
         <v>3875</v>
       </c>
     </row>
@@ -4577,15 +5402,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
           <t>4.2-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
         <v>3789</v>
       </c>
     </row>
@@ -4602,15 +5432,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
           <t>4.2-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
         <v>3473</v>
       </c>
     </row>
@@ -4627,15 +5462,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
           <t>4.2-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
         <v>3739</v>
       </c>
     </row>
@@ -4652,15 +5492,20 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
           <t>4.2-CUSTOM</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
         <v>3427</v>
       </c>
     </row>
@@ -4677,15 +5522,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
           <t>4.2-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
         <v>3444</v>
       </c>
     </row>
@@ -4702,15 +5552,20 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
           <t>4.2-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E171" t="n">
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
         <v>4305</v>
       </c>
     </row>
@@ -4727,15 +5582,20 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
           <t>4.2-DEVOPS</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
         <v>3790</v>
       </c>
     </row>
@@ -4752,15 +5612,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
           <t>4.2-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
         <v>3875</v>
       </c>
     </row>
@@ -4777,15 +5642,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
           <t>4.2-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
         <v>3552</v>
       </c>
     </row>
@@ -4802,15 +5672,20 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
           <t>4.2-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
         <v>3444</v>
       </c>
     </row>
@@ -4827,15 +5702,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
           <t>4.2-EMBEDDED</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
         <v>2920</v>
       </c>
     </row>
@@ -4852,15 +5732,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
           <t>4.2-ERP</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
         <v>3767</v>
       </c>
     </row>
@@ -4877,15 +5762,20 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
           <t>4.2-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E178" t="n">
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
         <v>3229</v>
       </c>
     </row>
@@ -4902,15 +5792,20 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
           <t>4.2-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
         <v>3552</v>
       </c>
     </row>
@@ -4927,15 +5822,20 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
           <t>4.2-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E180" t="n">
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
         <v>4521</v>
       </c>
     </row>
@@ -4952,15 +5852,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
           <t>4.2-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
         <v>3229</v>
       </c>
     </row>
@@ -4977,15 +5882,20 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
           <t>4.2-INFRAOPS</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
         <v>3229</v>
       </c>
     </row>
@@ -5002,15 +5912,20 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
           <t>4.2-JAVA</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E183" t="n">
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
         <v>3799</v>
       </c>
     </row>
@@ -5027,15 +5942,20 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
           <t>4.2-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E184" t="n">
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
         <v>4090</v>
       </c>
     </row>
@@ -5052,15 +5972,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
           <t>4.2-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
         <v>4413</v>
       </c>
     </row>
@@ -5077,15 +6002,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
           <t>4.2-PHP</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E186" t="n">
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
         <v>3121</v>
       </c>
     </row>
@@ -5102,15 +6032,20 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
           <t>4.2-PYTHON</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E187" t="n">
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
         <v>3767</v>
       </c>
     </row>
@@ -5127,15 +6062,20 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
           <t>4.3-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E188" t="n">
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
         <v>4456</v>
       </c>
     </row>
@@ -5152,15 +6092,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
           <t>4.3-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
         <v>4357</v>
       </c>
     </row>
@@ -5177,15 +6122,20 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
           <t>4.3-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E190" t="n">
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
         <v>3994</v>
       </c>
     </row>
@@ -5202,15 +6152,20 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
           <t>4.3-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E191" t="n">
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
         <v>4300</v>
       </c>
     </row>
@@ -5227,15 +6182,20 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
           <t>4.3-CUSTOM</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
         <v>3941</v>
       </c>
     </row>
@@ -5252,15 +6212,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
           <t>4.3-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
         <v>3961</v>
       </c>
     </row>
@@ -5277,15 +6242,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
           <t>4.3-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E194" t="n">
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
         <v>4951</v>
       </c>
     </row>
@@ -5302,15 +6272,20 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
           <t>4.3-DEVOPS</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E195" t="n">
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
         <v>4358</v>
       </c>
     </row>
@@ -5327,15 +6302,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
           <t>4.3-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E196" t="n">
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
         <v>4456</v>
       </c>
     </row>
@@ -5352,15 +6332,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
           <t>4.3-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E197" t="n">
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
         <v>4085</v>
       </c>
     </row>
@@ -5377,15 +6362,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
           <t>4.3-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
         <v>3961</v>
       </c>
     </row>
@@ -5402,15 +6392,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
           <t>4.3-EMBEDDED</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E199" t="n">
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
         <v>3358</v>
       </c>
     </row>
@@ -5427,15 +6422,20 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
           <t>4.3-ERP</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E200" t="n">
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
         <v>4332</v>
       </c>
     </row>
@@ -5452,15 +6452,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
           <t>4.3-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E201" t="n">
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
         <v>3713</v>
       </c>
     </row>
@@ -5477,15 +6482,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
           <t>4.3-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E202" t="n">
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
         <v>4085</v>
       </c>
     </row>
@@ -5502,15 +6512,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
           <t>4.3-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E203" t="n">
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
         <v>5199</v>
       </c>
     </row>
@@ -5527,15 +6542,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
           <t>4.3-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E204" t="n">
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
         <v>3713</v>
       </c>
     </row>
@@ -5552,15 +6572,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
           <t>4.3-INFRAOPS</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E205" t="n">
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
         <v>3713</v>
       </c>
     </row>
@@ -5577,15 +6602,20 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
           <t>4.3-JAVA</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E206" t="n">
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
         <v>4369</v>
       </c>
     </row>
@@ -5602,15 +6632,20 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
           <t>4.3-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E207" t="n">
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
         <v>4704</v>
       </c>
     </row>
@@ -5627,15 +6662,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
           <t>4.3-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E208" t="n">
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
         <v>5075</v>
       </c>
     </row>
@@ -5652,15 +6692,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
           <t>4.3-PHP</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E209" t="n">
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
         <v>3590</v>
       </c>
     </row>
@@ -5677,15 +6722,20 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
           <t>4.3-PYTHON</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E210" t="n">
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
         <v>4332</v>
       </c>
     </row>
@@ -5702,15 +6752,20 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
           <t>5.1-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E211" t="n">
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
         <v>5793</v>
       </c>
     </row>
@@ -5727,15 +6782,20 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
           <t>5.1-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E212" t="n">
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
         <v>5664</v>
       </c>
     </row>
@@ -5752,15 +6812,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
           <t>5.1-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E213" t="n">
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
         <v>5192</v>
       </c>
     </row>
@@ -5777,15 +6842,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
           <t>5.1-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E214" t="n">
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
         <v>5590</v>
       </c>
     </row>
@@ -5802,15 +6872,20 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
           <t>5.1-CUSTOM</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E215" t="n">
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
         <v>5123</v>
       </c>
     </row>
@@ -5827,15 +6902,20 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
           <t>5.1-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E216" t="n">
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
         <v>5149</v>
       </c>
     </row>
@@ -5852,15 +6932,20 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
           <t>5.1-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E217" t="n">
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
         <v>6436</v>
       </c>
     </row>
@@ -5877,15 +6962,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
           <t>5.1-DEVOPS</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E218" t="n">
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
         <v>5666</v>
       </c>
     </row>
@@ -5902,15 +6992,20 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
           <t>5.1-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E219" t="n">
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
         <v>5793</v>
       </c>
     </row>
@@ -5927,15 +7022,20 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
           <t>5.1-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E220" t="n">
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
         <v>5310</v>
       </c>
     </row>
@@ -5952,15 +7052,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
           <t>5.1-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E221" t="n">
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
         <v>5149</v>
       </c>
     </row>
@@ -5977,15 +7082,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
           <t>5.1-EMBEDDED</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E222" t="n">
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
         <v>4365</v>
       </c>
     </row>
@@ -6002,15 +7112,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
           <t>5.1-ERP</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E223" t="n">
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
         <v>5632</v>
       </c>
     </row>
@@ -6027,15 +7142,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
           <t>5.1-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E224" t="n">
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
         <v>4827</v>
       </c>
     </row>
@@ -6052,15 +7172,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
           <t>5.1-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E225" t="n">
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
         <v>5310</v>
       </c>
     </row>
@@ -6077,15 +7202,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
           <t>5.1-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E226" t="n">
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
         <v>6758</v>
       </c>
     </row>
@@ -6102,15 +7232,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
           <t>5.1-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E227" t="n">
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
         <v>4827</v>
       </c>
     </row>
@@ -6127,15 +7262,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
           <t>5.1-INFRAOPS</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E228" t="n">
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
         <v>4827</v>
       </c>
     </row>
@@ -6152,15 +7292,20 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
           <t>5.1-JAVA</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E229" t="n">
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
         <v>5680</v>
       </c>
     </row>
@@ -6177,15 +7322,20 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
           <t>5.1-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E230" t="n">
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
         <v>6115</v>
       </c>
     </row>
@@ -6202,15 +7352,20 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
           <t>5.1-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E231" t="n">
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
         <v>6597</v>
       </c>
     </row>
@@ -6227,15 +7382,20 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
           <t>5.1-PHP</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E232" t="n">
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -6252,15 +7412,20 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
           <t>5.1-PYTHON</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E233" t="n">
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
         <v>5632</v>
       </c>
     </row>
@@ -6277,15 +7442,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
           <t>5.2-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E234" t="n">
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
         <v>6662</v>
       </c>
     </row>
@@ -6302,15 +7472,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
           <t>5.2-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E235" t="n">
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
         <v>6514</v>
       </c>
     </row>
@@ -6327,15 +7502,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
           <t>5.2-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E236" t="n">
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
         <v>5971</v>
       </c>
     </row>
@@ -6352,15 +7532,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
           <t>5.2-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E237" t="n">
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
         <v>6429</v>
       </c>
     </row>
@@ -6377,15 +7562,20 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
           <t>5.2-CUSTOM</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E238" t="n">
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
         <v>5892</v>
       </c>
     </row>
@@ -6402,15 +7592,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
           <t>5.2-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E239" t="n">
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
         <v>5922</v>
       </c>
     </row>
@@ -6427,15 +7622,20 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
           <t>5.2-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E240" t="n">
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
         <v>7402</v>
       </c>
     </row>
@@ -6452,15 +7652,20 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
           <t>5.2-DEVOPS</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E241" t="n">
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
         <v>6516</v>
       </c>
     </row>
@@ -6477,15 +7682,20 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
           <t>5.2-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E242" t="n">
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
         <v>6662</v>
       </c>
     </row>
@@ -6502,15 +7712,20 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
           <t>5.2-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E243" t="n">
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
         <v>6107</v>
       </c>
     </row>
@@ -6527,15 +7742,20 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
           <t>5.2-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E244" t="n">
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
         <v>5922</v>
       </c>
     </row>
@@ -6552,15 +7772,20 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
           <t>5.2-EMBEDDED</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E245" t="n">
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
         <v>5020</v>
       </c>
     </row>
@@ -6577,15 +7802,20 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
           <t>5.2-ERP</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E246" t="n">
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
         <v>6477</v>
       </c>
     </row>
@@ -6602,15 +7832,20 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
           <t>5.2-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E247" t="n">
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
         <v>5551</v>
       </c>
     </row>
@@ -6627,15 +7862,20 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
           <t>5.2-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E248" t="n">
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
         <v>6107</v>
       </c>
     </row>
@@ -6652,15 +7892,20 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
           <t>5.2-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E249" t="n">
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
         <v>7772</v>
       </c>
     </row>
@@ -6677,15 +7922,20 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
           <t>5.2-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E250" t="n">
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
         <v>5551</v>
       </c>
     </row>
@@ -6702,15 +7952,20 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
           <t>5.2-INFRAOPS</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E251" t="n">
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
         <v>5551</v>
       </c>
     </row>
@@ -6727,15 +7982,20 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
           <t>5.2-JAVA</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E252" t="n">
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
         <v>6532</v>
       </c>
     </row>
@@ -6752,15 +8012,20 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
           <t>5.2-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E253" t="n">
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
         <v>7032</v>
       </c>
     </row>
@@ -6777,15 +8042,20 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
           <t>5.2-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E254" t="n">
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
         <v>7587</v>
       </c>
     </row>
@@ -6802,15 +8072,20 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
           <t>5.2-PHP</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E255" t="n">
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
         <v>5366</v>
       </c>
     </row>
@@ -6827,15 +8102,20 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
           <t>5.2-PYTHON</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E256" t="n">
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
         <v>6477</v>
       </c>
     </row>
@@ -6852,15 +8132,20 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
           <t>5.3-BIG-DATA-ENGINEER</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E257" t="n">
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
         <v>7661</v>
       </c>
     </row>
@@ -6877,15 +8162,20 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
           <t>5.3-CLOUD-INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E258" t="n">
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
         <v>7491</v>
       </c>
     </row>
@@ -6902,15 +8192,20 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
           <t>5.3-CRM-MULESOFT</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E259" t="n">
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
         <v>6867</v>
       </c>
     </row>
@@ -6927,15 +8222,20 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
           <t>5.3-CRM-SALESFORCE</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E260" t="n">
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
         <v>7393</v>
       </c>
     </row>
@@ -6952,15 +8252,20 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
           <t>5.3-CUSTOM</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E261" t="n">
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
         <v>6776</v>
       </c>
     </row>
@@ -6977,15 +8282,20 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
           <t>5.3-DATA-ANALYST</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E262" t="n">
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
         <v>6810</v>
       </c>
     </row>
@@ -7002,15 +8312,20 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
           <t>5.3-DATA-SCIENCE</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E263" t="n">
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
         <v>8512</v>
       </c>
     </row>
@@ -7027,15 +8342,20 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
           <t>5.3-DEVOPS</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E264" t="n">
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
         <v>7493</v>
       </c>
     </row>
@@ -7052,15 +8372,20 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
           <t>5.3-DOTNET-FULLSTACK</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E265" t="n">
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
         <v>7661</v>
       </c>
     </row>
@@ -7077,15 +8402,20 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
           <t>5.3-DOTNET-WEB</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E266" t="n">
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
         <v>7023</v>
       </c>
     </row>
@@ -7102,15 +8432,20 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
           <t>5.3-DOTNET-WINDOWS</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E267" t="n">
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
         <v>6810</v>
       </c>
     </row>
@@ -7127,15 +8462,20 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
           <t>5.3-EMBEDDED</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E268" t="n">
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
         <v>5773</v>
       </c>
     </row>
@@ -7152,15 +8492,20 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
           <t>5.3-ERP</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E269" t="n">
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
         <v>7448</v>
       </c>
     </row>
@@ -7177,15 +8522,20 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
           <t>5.3-FASTAPPDEV</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E270" t="n">
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
         <v>6384</v>
       </c>
     </row>
@@ -7202,15 +8552,20 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
           <t>5.3-FRONTEND-ANGULAR2X</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E271" t="n">
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
         <v>7023</v>
       </c>
     </row>
@@ -7227,15 +8582,20 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
           <t>5.3-GENERATIVE-AI</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E272" t="n">
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
         <v>8938</v>
       </c>
     </row>
@@ -7252,15 +8612,20 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
           <t>5.3-INDUSTRIAL-PLANT-ENGINEER</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E273" t="n">
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
         <v>6384</v>
       </c>
     </row>
@@ -7277,15 +8642,20 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
           <t>5.3-INFRAOPS</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E274" t="n">
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
         <v>6384</v>
       </c>
     </row>
@@ -7302,15 +8672,20 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
           <t>5.3-JAVA</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E275" t="n">
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
         <v>7511</v>
       </c>
     </row>
@@ -7327,15 +8702,20 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
           <t>5.3-JAVA-FULLSTACK</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E276" t="n">
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
         <v>8087</v>
       </c>
     </row>
@@ -7352,15 +8732,20 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
           <t>5.3-MACHINE-LEARNING</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E277" t="n">
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
         <v>8725</v>
       </c>
     </row>
@@ -7377,15 +8762,20 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
           <t>5.3-PHP</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E278" t="n">
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
         <v>6171</v>
       </c>
     </row>
@@ -7402,15 +8792,20 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
+          <t>Pan-India</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
           <t>5.3-PYTHON</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="E279" t="n">
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
         <v>7448</v>
       </c>
     </row>
